--- a/data/trans_camb/IP07_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,99</t>
+          <t>-4,19; 0,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,66</t>
+          <t>-3,32; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,82</t>
+          <t>-2,39; 5,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,96</t>
+          <t>-2,6; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,75</t>
+          <t>-2,41; 4,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,19</t>
+          <t>-2,6; 4,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,75</t>
+          <t>-2,57; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,3</t>
+          <t>-2,36; 2,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,87</t>
+          <t>-2,03; 2,95</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-51,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-18,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>22,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>19,64%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-51,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-18,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,75; 396,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 382,9</t>
+          <t>-82,4; 347,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,32; 408,08</t>
+          <t>-76,4; 474,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-91,79; 153,43</t>
+          <t>-79,78; 466,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,12; 295,99</t>
+          <t>-74,75; 502,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,49; 484,09</t>
+          <t>-81,38; 606,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 128,15</t>
+          <t>-71,65; 109,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 168,88</t>
+          <t>-68,28; 141,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 194,36</t>
+          <t>-61,11; 196,04</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,77</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,9</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-1,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,95</t>
+          <t>-7,37; -1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,95</t>
+          <t>-6,89; -0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 13,61</t>
+          <t>-6,97; -1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -1,92</t>
+          <t>-3,23; 0,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; -1,09</t>
+          <t>-2,35; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -1,04</t>
+          <t>-1,86; 4,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,84</t>
+          <t>-4,75; -0,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,28</t>
+          <t>-4,27; -0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,68</t>
+          <t>-3,62; 0,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-74,45%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-67,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-65,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-43,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-8,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>159,09%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-74,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-67,69%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,25%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,69%</t>
+          <t>-37,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,44; 139,19</t>
+          <t>-90,54; -29,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,22; 218,93</t>
+          <t>-88,85; -9,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 1363,91</t>
+          <t>-87,0; -19,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-92,11; -34,18</t>
+          <t>-88,51; 110,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,54; -15,81</t>
+          <t>-69,7; 188,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,57; -16,68</t>
+          <t>-62,72; 327,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,74; -24,39</t>
+          <t>-86,24; -27,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 1,72</t>
+          <t>-78,08; -7,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 172,64</t>
+          <t>-69,09; 10,48</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,25</t>
+          <t>-1,58; 4,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,57</t>
+          <t>-1,86; 4,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,1</t>
+          <t>-3,14; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,05</t>
+          <t>-1,34; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,24</t>
+          <t>-2,2; 2,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,92</t>
+          <t>-1,38; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,64</t>
+          <t>-0,49; 3,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,62</t>
+          <t>-1,33; 2,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,72</t>
+          <t>-1,75; 2,16</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>71,46%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46,18%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-32,54%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>78,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32,89%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46,18%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-33,35%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-4,46%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,9; 721,21</t>
+          <t>-51,77; 498,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 414,22</t>
+          <t>-55,61; 470,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 566,67</t>
+          <t>-100,0; 341,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 633,3</t>
+          <t>-56,81; 770,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 538,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 308,72</t>
+          <t>-61,24; 617,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 372,73</t>
+          <t>-24,33; 325,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,65; 251,22</t>
+          <t>-47,12; 223,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 166,23</t>
+          <t>-62,66; 199,62</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,51</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,34</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0,73</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,92</t>
+          <t>-2,29; 3,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,13</t>
+          <t>-3,98; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,82</t>
+          <t>-2,13; 4,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,75</t>
+          <t>-0,02; 4,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,62</t>
+          <t>-1,06; 2,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,15</t>
+          <t>-0,93; 3,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,04</t>
+          <t>-0,52; 3,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,83</t>
+          <t>-1,95; 0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,75</t>
+          <t>-0,93; 2,72</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-52,34%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>244,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>48,61%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>104,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-52,34%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>101,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,82; —</t>
+          <t>-58,02; 221,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-89,87; 77,72</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-53,93; 307,45</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-48,08; —</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-51,72; 214,93</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-88,47; 74,26</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-55,83; 240,84</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 275,84</t>
+          <t>-28,22; 281,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 100,46</t>
+          <t>-77,22; 78,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 267,27</t>
+          <t>-40,72; 263,27</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,96</t>
+          <t>-2,51; 0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,4</t>
+          <t>-2,99; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,02</t>
+          <t>-2,77; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,36</t>
+          <t>-0,6; 1,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,09</t>
+          <t>-0,97; 1,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,36</t>
+          <t>-0,42; 2,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,76</t>
+          <t>-1,15; 0,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,23</t>
+          <t>-1,49; 0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,85</t>
+          <t>-1,11; 0,85</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-29,26%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-40,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,76%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>37,05%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-29,26%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-40,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>-5,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 159,34</t>
+          <t>-59,51; 14,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 122,02</t>
+          <t>-65,92; 3,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 335,25</t>
+          <t>-61,76; 19,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 16,56</t>
+          <t>-28,29; 162,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,69; -0,86</t>
+          <t>-41,59; 117,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 14,89</t>
+          <t>-19,61; 218,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 35,79</t>
+          <t>-36,2; 31,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 12,51</t>
+          <t>-48,15; 13,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,32</t>
+          <t>-35,58; 39,58</t>
         </is>
       </c>
     </row>
